--- a/Semestre 1/Algoritmos/Aula 18 - 08/Teste de Mesa - Exercicio 2.xlsx
+++ b/Semestre 1/Algoritmos/Aula 18 - 08/Teste de Mesa - Exercicio 2.xlsx
@@ -24,7 +24,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="29">
+  <si>
+    <t>Fimalgoritmo</t>
+  </si>
   <si>
     <t>TESTE DE MESA</t>
   </si>
@@ -96,6 +99,18 @@
   </si>
   <si>
     <t>Calcula a Prestação</t>
+  </si>
+  <si>
+    <t>Exibe mensagem</t>
+  </si>
+  <si>
+    <t>Exibe valor da prestação</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inicio </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fim </t>
   </si>
 </sst>
 </file>
@@ -423,27 +438,27 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
@@ -451,7 +466,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -463,7 +478,13 @@
         <v>0</v>
       </c>
       <c r="G3" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="M3">
+        <v>1</v>
+      </c>
+      <c r="N3" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
@@ -482,11 +503,14 @@
       <c r="E4">
         <v>0</v>
       </c>
+      <c r="G4" t="s">
+        <v>25</v>
+      </c>
       <c r="M4">
         <v>1</v>
       </c>
       <c r="N4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
@@ -500,19 +524,19 @@
         <v>0</v>
       </c>
       <c r="D5" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="G5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M5">
         <v>2</v>
       </c>
       <c r="N5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
@@ -520,22 +544,25 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="C6">
         <v>0</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E6">
         <v>0</v>
+      </c>
+      <c r="G6" t="s">
+        <v>25</v>
       </c>
       <c r="M6">
         <v>3</v>
       </c>
       <c r="N6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
@@ -552,16 +579,16 @@
         <v>30</v>
       </c>
       <c r="E7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M7">
         <v>4</v>
       </c>
       <c r="N7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
@@ -572,7 +599,7 @@
         <v>30</v>
       </c>
       <c r="C8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D8">
         <v>30</v>
@@ -581,29 +608,65 @@
         <v>15</v>
       </c>
       <c r="G8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M8">
         <v>5</v>
       </c>
       <c r="N8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>30</v>
+      </c>
+      <c r="C9">
+        <v>165</v>
+      </c>
+      <c r="D9">
+        <v>30</v>
+      </c>
+      <c r="E9">
+        <v>15</v>
+      </c>
+      <c r="G9" t="s">
+        <v>26</v>
+      </c>
       <c r="M9">
         <v>6</v>
       </c>
       <c r="N9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>30</v>
+      </c>
+      <c r="C10">
+        <v>165</v>
+      </c>
+      <c r="D10">
+        <v>30</v>
+      </c>
+      <c r="E10">
+        <v>15</v>
+      </c>
+      <c r="G10" t="s">
+        <v>28</v>
+      </c>
       <c r="M10">
         <v>7</v>
       </c>
       <c r="N10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
@@ -611,17 +674,25 @@
         <v>8</v>
       </c>
       <c r="N11" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M12">
+        <v>9</v>
+      </c>
+      <c r="N12" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
